--- a/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Differential_Fairness_of_sensitive_attribute.xlsx
+++ b/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Differential_Fairness_of_sensitive_attribute.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,28 +441,78 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>P-Value</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Significance</t>
+          <t>P-Value (raw)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-Value (Bonferroni)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reject (Bonf@0.05)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Partial_R2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cohen_f2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (raw)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (bonf)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Number of Items</t>
+          <t>hit@5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.73111230797002</v>
+        <v>0.8308587974196802</v>
       </c>
       <c r="C2" t="n">
-        <v>2.51020606247441e-34</v>
-      </c>
-      <c r="D2" t="inlineStr">
+        <v>8.974464690228194</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.690343428462992e-18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.718755542618582e-17</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.08384963795885152</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3545056007624276</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -471,16 +521,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Number of Items</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.375197384932989</v>
+        <v>1.823896635317745</v>
       </c>
       <c r="C3" t="n">
-        <v>9.202499287457809e-17</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>8.880301089302755</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.688342043179228e-18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8.114352494994301e-17</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.08224325574985097</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3477140211692602</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -489,16 +559,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dataset_BX</t>
+          <t>Number of Ratings</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8187121594304838</v>
+        <v>-1.707512825895594</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001240865695677564</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>-4.834994030926861</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.571073621565832e-06</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.45636196744483e-05</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.02587752726749624</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1094068927848178</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -507,16 +597,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Difference between Sensitive Attribute Percentage</t>
+          <t>Rating per User</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7459315104999155</v>
+        <v>0.6221376183833986</v>
       </c>
       <c r="C5" t="n">
-        <v>6.504117118208687e-05</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>4.494810931934225</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.893163950374487e-06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0001736496069082387</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02244306896643821</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.09488644006792499</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -525,16 +635,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Age</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7356423075147689</v>
+        <v>-0.9481683529729837</v>
       </c>
       <c r="C6" t="n">
-        <v>1.333621159804966e-16</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>-4.126361787734854</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.035395051810585e-05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0008877869113983288</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01898144005726411</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0802511134769435</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -543,236 +673,568 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Standart Deviation of Rating</t>
+          <t>Number of Users</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6809097378386162</v>
+        <v>0.7927751386150416</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007060411283167995</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>**</t>
+        <v>3.317470093409006</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0009456078341439338</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02080337235116654</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01235189512171769</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.05222224099319184</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Gender</t>
+          <t>Gini User</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6395550774182084</v>
+        <v>0.6550523160257464</v>
       </c>
       <c r="C8" t="n">
-        <v>4.328184888623461e-15</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>***</t>
+        <v>3.190400514074007</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.001471076580770322</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.03236368477694709</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01143439620574841</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.048343172313561</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rating per User</t>
+          <t>Difference between Sensitive Attribute Percentage</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6349353308418486</v>
+        <v>0.6575304386237382</v>
       </c>
       <c r="C9" t="n">
-        <v>3.582045093260126e-13</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>2.144958175153473</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03222936586869456</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7090460491112804</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005201041346706715</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02198934106441005</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dataset_ml1m</t>
+          <t>Mean Rating</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5564852255024979</v>
+        <v>1.662072872179356</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06599309746275576</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>2.110327952507681</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0351117861632819</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7724592955922018</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005035294842930618</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02128858593504083</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gini User</t>
+          <t>Gini Item</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1583646884446606</v>
+        <v>0.6378443289572479</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1993399895780301</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>2.059935639744204</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.03969828219816744</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8733622083596837</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.004798831580287469</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02028884934676014</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skewness of Long Tail Items</t>
+          <t>Standart Deviation of Rating</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.137027380202545</v>
+        <v>0.6970054173943061</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1030589533861864</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>1.669016640406733</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.09546977126714658</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.003155484744816941</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01334098801603612</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hit@5</t>
+          <t>Model Name_NFCF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06027138906840966</v>
+        <v>519203840561.9497</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0831878025859875</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>1.450598474446894</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1472480370117882</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.002385473108900177</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01008547679106588</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mean Rating</t>
+          <t>Dataset_BX</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02054763855685682</v>
+        <v>774296821588.1216</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9653894564951172</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>1.450598474446573</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1472480370118778</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.002385473108899123</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.01008547679106142</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skewness of Popularity Bias</t>
+          <t>Model Name_PFCN_MLP</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.00790196129886378</v>
+        <v>519203840561.6669</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9261502606482794</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>1.450598474446102</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1472480370120088</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.002385473108897579</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.01008547679105489</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gini Item</t>
+          <t>const</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03361818112956461</v>
+        <v>1277276762387.394</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8559003541716881</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>1.450598474445435</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1472480370121947</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.002385473108895389</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01008547679104563</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Number of Users</t>
+          <t>Sensitive Feature_Gender</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.161720357767981</v>
+        <v>-2570777424535.991</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2588500903471422</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>-1.450598474445259</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1472480370122436</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002385473108894813</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0100854767910432</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Sensitive Feature_Age</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.2011900157533175</v>
+        <v>-2570777424535.862</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2605874031349835</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>-1.450598474445187</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1472480370122637</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.002385473108894578</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0100854767910422</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rating per Item</t>
+          <t>Dataset_ml1m</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3073327225490984</v>
+        <v>774296821586.8955</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04273380067027997</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>1.450598474444226</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1472480370125315</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.002385473108891423</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.01008547679102886</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Model Name_FOCF</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.7862970848892317</v>
+        <v>519203840560.6307</v>
       </c>
       <c r="C20" t="n">
-        <v>3.022361989648357e-08</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>1.450598474443201</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1472480370128169</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.00238547310888806</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.01008547679101465</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Number of Ratings</t>
+          <t>Rating per Item</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.032486191403938</v>
+        <v>-0.3520067801944605</v>
       </c>
       <c r="C21" t="n">
-        <v>1.820194166818125e-06</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-1.399212380284789</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1621016762528916</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.002219828766873428</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.009385153588574446</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2400614597539984</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8145874909479757</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.4155288558890951</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0007534691066911603</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.003185571516177099</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.06032296396419645</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4323381362802562</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6656015941502839</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0002123597393104227</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0008978299584184044</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.03330626971659179</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2324471446379985</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8162447831861739</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6.139586105584615e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0002595738889011106</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
